--- a/data/trans_orig/IP41-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP41-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>110066</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>104567</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>114062</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>91,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>87,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>98868</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>94648</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>101519</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>94515</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>101604</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>94,97%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>90,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>110066</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>104090</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>114220</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>91,78%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>200643</t>
+          <t>202197</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>214023</t>
+          <t>214213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9860</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5864</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15359</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>5232</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2581</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9452</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2496</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9585</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>5,03%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9860</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5706</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15836</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23383</t>
+          <t>21829</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>119926</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>119926</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>119926</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104100</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104100</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104100</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>119926</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>119926</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>119926</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>234770</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>227632</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>240618</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>92,98%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>90,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>95,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>227081</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>218466</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>233511</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>219457</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>234005</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>90,72%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>87,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>93,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>234770</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>227271</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>240516</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>92,98%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>450451</t>
+          <t>451293</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>470852</t>
+          <t>471156</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17723</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11875</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>24861</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>23232</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16802</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31847</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>16308</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>30856</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>9,28%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17723</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>11977</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>25222</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31954</t>
+          <t>31650</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52355</t>
+          <t>51513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>252493</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>252493</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>252493</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>250313</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>250313</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>250313</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>252493</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>252493</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>252493</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>128189</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>121806</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>132458</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>92,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>87,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>95,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>107166</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>99883</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>112792</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>100462</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>113592</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>85,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>79,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>89,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>128189</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>122067</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>132331</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>92,27%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>225415</t>
+          <t>225841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>242698</t>
+          <t>243450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10742</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6473</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17125</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12,33%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>18404</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12778</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25687</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>11978</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>25108</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>14,66%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10742</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>6600</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>16864</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>7,73%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21803</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39086</t>
+          <t>38660</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>138931</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>138931</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>138931</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>125570</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>125570</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>125570</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>138931</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>138931</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>138931</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>188112</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>181270</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>193575</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>92,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>88,73%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>94,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>178358</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>172320</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>183672</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>171608</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>183156</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>93,24%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>90,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>188112</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>181783</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>193525</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>92,08%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>356233</t>
+          <t>357187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>373858</t>
+          <t>374243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16177</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10714</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23019</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>12922</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7608</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18960</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>8124</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>19672</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>6,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>16177</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>10764</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>22506</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21712</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39337</t>
+          <t>38383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204289</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204289</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204289</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>191280</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>191280</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>191280</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204289</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204289</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204289</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>661138</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>648186</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>672164</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>916</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>611473</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>597408</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>622663</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>598853</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>622097</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>91,09%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>89,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>661138</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>648998</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>671824</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1255897</t>
+          <t>1255890</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1287529</t>
+          <t>1289194</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>54502</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>43476</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>67454</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>59790</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>48600</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>73855</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>49166</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>72410</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>8,91%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>54502</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>43816</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>66642</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99374</t>
+          <t>97709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131006</t>
+          <t>131013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>715640</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>715640</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>715640</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1004</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>671263</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>671263</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>671263</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1075</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>715640</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>715640</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>715640</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>133186</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>126077</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>137994</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>91,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>86,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>94,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>138020</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>132626</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>142007</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>132594</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>141520</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>94,04%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>90,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>133186</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>126535</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>137908</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>263932</t>
+          <t>263359</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277838</t>
+          <t>277585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12804</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7996</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19913</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13,64%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8741</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4754</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14135</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5241</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14167</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>5,96%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12804</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8082</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19455</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14913</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28819</t>
+          <t>29392</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>240365</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>230658</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>248915</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>89,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>85,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>92,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>207385</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>197558</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>214366</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>198212</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>214608</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>87,78%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>83,62%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>90,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>240365</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>230559</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>247045</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>89,36%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>435531</t>
+          <t>435183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>458615</t>
+          <t>459036</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28626</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20076</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38333</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>28865</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21884</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>38692</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>21642</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>38038</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>12,22%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>28626</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>21946</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>38432</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46626</t>
+          <t>46205</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69710</t>
+          <t>70058</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>140751</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>132955</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>146312</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>88,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>83,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>92,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>137740</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>130265</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>143551</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>130434</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>143612</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>88,11%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>140751</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>132386</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>146347</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>267300</t>
+          <t>268395</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>286378</t>
+          <t>287549</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17820</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12259</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25616</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>11,24%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>18585</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12774</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>26060</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12713</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>25891</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>11,89%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>16,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>17820</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>12224</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>26185</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>11,24%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>27347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47596</t>
+          <t>46501</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156325</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156325</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156325</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>150930</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>141979</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>158223</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83,87%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>78,9%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>150578</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>143226</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>156901</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>142298</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>156483</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>87,88%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>83,59%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>91,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>150930</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>142128</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>158488</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>83,87%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>289903</t>
+          <t>290539</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>311106</t>
+          <t>311615</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29025</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21732</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>37976</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21,1%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>20759</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14436</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28111</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>14854</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>29039</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>12,12%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>29025</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>21467</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>37827</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>16,13%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40186</t>
+          <t>39677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61389</t>
+          <t>60753</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>665232</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>649247</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>679152</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>88,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>86,16%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>90,13%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>912</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>633723</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>620351</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>647122</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>619897</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>647022</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>89,17%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>87,29%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>91,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>665232</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>649515</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>678391</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>88,28%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1277477</t>
+          <t>1278637</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1317922</t>
+          <t>1317666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>88275</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>74355</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>104260</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>11,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13,84%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>76950</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>63551</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>90322</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>63651</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>90776</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>10,83%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>88275</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>75116</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>103992</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>146258</t>
+          <t>146514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>186703</t>
+          <t>185543</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>710673</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>710673</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>710673</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>109378</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>102158</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>114218</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>88,09%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>82,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>116768</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>110155</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>121738</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>110452</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>121706</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>88,69%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>83,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>92,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>109378</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>102962</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>114753</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>88,09%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>217502</t>
+          <t>217181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>233831</t>
+          <t>233478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14786</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9946</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22006</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>17,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14886</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9916</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21499</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9948</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>21202</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>11,31%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14786</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9411</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21202</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38316</t>
+          <t>38637</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,74 +4959,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>214364</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>203582</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>223783</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>83,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>79,08%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>86,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>182346</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>173810</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>173497</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>189462</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>86,62%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>82,56%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>82,41%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>90,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>214364</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>203296</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>223636</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>83,27%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>78,97%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>86,87%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>604</t>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>383474</t>
+          <t>382599</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>408103</t>
+          <t>407809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,15%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>43063</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33644</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>53845</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>28171</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>21055</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>36707</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>37020</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>13,38%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>10,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>17,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>43063</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>33791</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>54131</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>16,73%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>13,13%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59841</t>
+          <t>60135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84470</t>
+          <t>85345</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>257427</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>257427</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>257427</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>257427</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>257427</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>257427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>153389</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>142981</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>161072</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>76,09%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>85,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>149291</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>139855</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>158056</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>138543</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>158023</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>79,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>74,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>153389</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>143820</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>161306</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>81,62%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>289672</t>
+          <t>288990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>313851</t>
+          <t>313884</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,5%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34530</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26847</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>44938</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>23,91%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>38707</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>29942</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>48143</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>29975</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>49455</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>20,59%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>25,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>34530</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>26613</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>44099</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62067</t>
+          <t>62034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86246</t>
+          <t>86928</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187919</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187919</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187919</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>187998</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>187998</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>187998</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187919</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187919</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187919</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>145639</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>135671</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>77,95%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>143871</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>134890</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>152273</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>135562</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>151297</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>83,02%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>77,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>87,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>145639</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>136925</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>152866</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>83,68%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>276166</t>
+          <t>275714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>300633</t>
+          <t>300971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28409</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20950</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38377</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>22,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>29430</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>38411</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>22004</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>37739</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>16,98%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>28409</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>21182</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>37123</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>16,32%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46715</t>
+          <t>46377</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71182</t>
+          <t>71634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>622770</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>605446</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>638865</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>83,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>81,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>85,92%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>896</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>592276</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>576591</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>607939</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>574859</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>607310</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>84,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>81,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>86,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>893</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>622770</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>604626</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>638256</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1192569</t>
+          <t>1189699</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1236573</t>
+          <t>1236418</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,45%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>120788</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>104693</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>138112</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>18,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>111194</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>95531</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>126879</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>96160</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>128611</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>15,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>120788</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>105302</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>138932</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>16,24%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>210455</t>
+          <t>210610</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>254459</t>
+          <t>257329</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>743558</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>743558</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>743558</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>703470</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>703470</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>703470</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>743558</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>743558</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>743558</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
